--- a/00_output/kwh_kw_ratio.xlsx
+++ b/00_output/kwh_kw_ratio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,96 +447,6 @@
           <t>multifamily_li</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,20 +457,6 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
-        <is>
-          <t>central_ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>room_ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
         <is>
           <t>fridge</t>
         </is>

--- a/00_output/kwh_kw_ratio.xlsx
+++ b/00_output/kwh_kw_ratio.xlsx
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>refrigerator</t>
         </is>
       </c>
     </row>

--- a/00_output/kwh_kw_ratio.xlsx
+++ b/00_output/kwh_kw_ratio.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,54 +458,73 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>enduse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>furnace</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>refrigerator</t>
         </is>
       </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/kwh_kw_ratio.xlsx
+++ b/00_output/kwh_kw_ratio.xlsx
@@ -460,7 +460,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
